--- a/diseases/d002/2005-2009.xlsx
+++ b/diseases/d002/2005-2009.xlsx
@@ -1288,9 +1288,6 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -1436,9 +1433,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2128,9 +2122,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2276,9 +2267,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2968,9 +2956,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3116,9 +3101,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3808,9 +3790,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -3956,9 +3935,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4648,9 +4624,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4796,9 +4769,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5488,9 +5458,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5636,9 +5603,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -6476,9 +6440,6 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -6624,9 +6585,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7316,9 +7274,6 @@
       <c r="O41" t="n">
         <v>8</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.01671833887253696</v>
       </c>
@@ -7464,9 +7419,6 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -8156,9 +8108,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.00208979235906712</v>
       </c>
@@ -8304,9 +8253,6 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -8996,9 +8942,6 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
@@ -9144,9 +9087,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -9836,9 +9776,6 @@
       <c r="O56" t="n">
         <v>2</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.004179584718134241</v>
       </c>
@@ -9984,9 +9921,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -10676,9 +10610,6 @@
       <c r="O61" t="n">
         <v>3</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.00626937707720136</v>
       </c>
@@ -10824,9 +10755,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -11743,9 +11671,6 @@
       <c r="O67" t="n">
         <v>2</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -11891,9 +11816,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12583,9 +12505,6 @@
       <c r="O72" t="n">
         <v>3</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.006249151482400281</v>
       </c>
@@ -12731,9 +12650,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13423,9 +13339,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -13571,9 +13484,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -14263,9 +14173,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14411,9 +14318,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -15103,9 +15007,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -15251,9 +15152,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16091,9 +15989,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -16239,9 +16134,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -16931,9 +16823,6 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
@@ -17079,9 +16968,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -17771,9 +17657,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -17919,9 +17802,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -18611,9 +18491,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -18759,9 +18636,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19451,9 +19325,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -19599,9 +19470,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -20291,9 +20159,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -20439,9 +20304,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21131,9 +20993,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -21279,9 +21138,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -22198,9 +22054,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -22346,9 +22199,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -23038,9 +22888,6 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -23186,9 +23033,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -23878,9 +23722,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -24026,9 +23867,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -24718,9 +24556,6 @@
       <c r="O144" t="n">
         <v>1</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -24866,9 +24701,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -25558,9 +25390,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -25706,9 +25535,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -26398,9 +26224,6 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -26546,9 +26369,6 @@
       <c r="O155" t="n">
         <v>1</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -27238,9 +27058,6 @@
       <c r="O159" t="n">
         <v>2</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.004151262154415599</v>
       </c>
@@ -27386,9 +27203,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -28078,9 +27892,6 @@
       <c r="O164" t="n">
         <v>1</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -28226,9 +28037,6 @@
       <c r="O165" t="n">
         <v>0</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0</v>
       </c>
@@ -28918,9 +28726,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -29066,9 +28871,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -29758,9 +29560,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -29906,9 +29705,6 @@
       <c r="O175" t="n">
         <v>0</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0</v>
       </c>
@@ -30598,9 +30394,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -30746,9 +30539,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -31438,9 +31228,6 @@
       <c r="O184" t="n">
         <v>1</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -31586,9 +31373,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -32505,9 +32289,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -32949,9 +32730,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -33393,9 +33171,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -33837,9 +33612,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -34281,9 +34053,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -34873,9 +34642,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -35317,9 +35083,6 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
@@ -35761,9 +35524,6 @@
       <c r="O212" t="n">
         <v>1</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -36205,9 +35965,6 @@
       <c r="O215" t="n">
         <v>2</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -36649,9 +36406,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -37093,9 +36847,6 @@
       <c r="O221" t="n">
         <v>1</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -37537,9 +37288,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -38208,9 +37956,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -38652,9 +38397,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -39096,9 +38838,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -39540,9 +39279,6 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
@@ -39984,9 +39720,6 @@
       <c r="O240" t="n">
         <v>0</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
@@ -40428,9 +40161,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -40872,9 +40602,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -41316,9 +41043,6 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -41760,9 +41484,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -42352,9 +42073,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -42796,9 +42514,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -43238,9 +42953,6 @@
         <v>0</v>
       </c>
       <c r="O262" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q262" t="n">
         <v>0</v>
       </c>
       <c r="R262" t="n">
